--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.423288089363007</v>
+        <v>1.206284314521489</v>
       </c>
       <c r="D2" t="n">
-        <v>7.687948698777899</v>
+        <v>1.249291663551409</v>
       </c>
       <c r="E2" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F2" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4196760369288</v>
+        <v>2.99319735600093</v>
       </c>
       <c r="D3" t="n">
-        <v>19.14716876980717</v>
+        <v>3.111414925093666</v>
       </c>
       <c r="E3" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F3" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.259590080052808</v>
+        <v>1.017183388008581</v>
       </c>
       <c r="D4" t="n">
-        <v>6.96750382193068</v>
+        <v>1.132219371063736</v>
       </c>
       <c r="E4" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F4" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.8856283341495</v>
+        <v>3.556414604299293</v>
       </c>
       <c r="D5" t="n">
-        <v>21.17990811453141</v>
+        <v>3.441735068611354</v>
       </c>
       <c r="E5" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F5" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.11227755006927</v>
+        <v>4.405745101886255</v>
       </c>
       <c r="D6" t="n">
-        <v>27.62164628697762</v>
+        <v>4.488517521633864</v>
       </c>
       <c r="E6" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F6" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.27507179047007</v>
+        <v>1.832199165951387</v>
       </c>
       <c r="D7" t="n">
-        <v>10.32204349110282</v>
+        <v>1.677332067304209</v>
       </c>
       <c r="E7" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F7" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.30635229320539</v>
+        <v>2.487282247645876</v>
       </c>
       <c r="D8" t="n">
-        <v>15.31666636525889</v>
+        <v>2.48895828435457</v>
       </c>
       <c r="E8" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F8" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.32304529377586</v>
+        <v>2.164994860238577</v>
       </c>
       <c r="D9" t="n">
-        <v>12.98775391349865</v>
+        <v>2.110510010943531</v>
       </c>
       <c r="E9" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F9" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.78687422330497</v>
+        <v>3.052867061287058</v>
       </c>
       <c r="D10" t="n">
-        <v>31.66642815239451</v>
+        <v>5.145794574764107</v>
       </c>
       <c r="E10" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F10" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.659077299815269</v>
+        <v>1.407100061219981</v>
       </c>
       <c r="D11" t="n">
-        <v>22.75308016333721</v>
+        <v>3.697375526542296</v>
       </c>
       <c r="E11" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F11" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>2.04139666877266</v>
+        <v>0.3317269586755573</v>
       </c>
       <c r="D12" t="n">
-        <v>25.48025002407626</v>
+        <v>4.140540628912392</v>
       </c>
       <c r="E12" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F12" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.84638752111383</v>
+        <v>2.737537972180997</v>
       </c>
       <c r="D13" t="n">
-        <v>26.98957193658564</v>
+        <v>4.385805439695166</v>
       </c>
       <c r="E13" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F13" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.6400048795597</v>
+        <v>3.029000792928451</v>
       </c>
       <c r="D14" t="n">
-        <v>13.27573864067322</v>
+        <v>2.157307529109398</v>
       </c>
       <c r="E14" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F14" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.40956570700884</v>
+        <v>1.366554427388937</v>
       </c>
       <c r="D15" t="n">
-        <v>8.349849703504191</v>
+        <v>1.356850576819431</v>
       </c>
       <c r="E15" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F15" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.46483900255355</v>
+        <v>4.625536337914952</v>
       </c>
       <c r="D16" t="n">
-        <v>16.94932648033384</v>
+        <v>2.75426555305425</v>
       </c>
       <c r="E16" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F16" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.21218372287282</v>
+        <v>2.634479854966834</v>
       </c>
       <c r="D17" t="n">
-        <v>13.97917635094861</v>
+        <v>2.271616157029149</v>
       </c>
       <c r="E17" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F17" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>26.66241617913709</v>
+        <v>4.332642629109777</v>
       </c>
       <c r="D18" t="n">
-        <v>22.1472345903501</v>
+        <v>3.598925620931892</v>
       </c>
       <c r="E18" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F18" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.81855324286227</v>
+        <v>2.57051490196512</v>
       </c>
       <c r="D19" t="n">
-        <v>16.81389906322053</v>
+        <v>2.732258597773336</v>
       </c>
       <c r="E19" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F19" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>4.868861016230515</v>
+        <v>0.7911899151374588</v>
       </c>
       <c r="D20" t="n">
-        <v>3.794805488670654</v>
+        <v>0.6166558919089814</v>
       </c>
       <c r="E20" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F20" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>12.48842302118862</v>
+        <v>2.02936874094315</v>
       </c>
       <c r="D21" t="n">
-        <v>11.47269675878638</v>
+        <v>1.864313223302787</v>
       </c>
       <c r="E21" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F21" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.9587533736435</v>
+        <v>5.843297423217069</v>
       </c>
       <c r="D22" t="n">
-        <v>36.35232156287208</v>
+        <v>5.907252253966714</v>
       </c>
       <c r="E22" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F22" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>24.39740943862804</v>
+        <v>3.964579033777056</v>
       </c>
       <c r="D23" t="n">
-        <v>25.12359249639284</v>
+        <v>4.082583780663836</v>
       </c>
       <c r="E23" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F23" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>3.417552311892185</v>
+        <v>0.5553522506824801</v>
       </c>
       <c r="D24" t="n">
-        <v>5.993251806437254</v>
+        <v>0.9739034185460538</v>
       </c>
       <c r="E24" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F24" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>13.81223290340044</v>
+        <v>2.244487846802572</v>
       </c>
       <c r="D25" t="n">
-        <v>7.648529270389178</v>
+        <v>1.242886006438241</v>
       </c>
       <c r="E25" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F25" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>11.26275926529874</v>
+        <v>1.830198380611045</v>
       </c>
       <c r="D26" t="n">
-        <v>11.31434691703953</v>
+        <v>1.838581374018925</v>
       </c>
       <c r="E26" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F26" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>25.16188580192746</v>
+        <v>4.088806442813212</v>
       </c>
       <c r="D27" t="n">
-        <v>28.51204050380559</v>
+        <v>4.633206581868408</v>
       </c>
       <c r="E27" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F27" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>15.80141932394211</v>
+        <v>2.567730640140593</v>
       </c>
       <c r="D28" t="n">
-        <v>15.89987776134737</v>
+        <v>2.583730136218948</v>
       </c>
       <c r="E28" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F28" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>10.34241681192415</v>
+        <v>1.680642731937675</v>
       </c>
       <c r="D29" t="n">
-        <v>10.46137524826674</v>
+        <v>1.699973477843345</v>
       </c>
       <c r="E29" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F29" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>9.014395195250639</v>
+        <v>1.464839219228229</v>
       </c>
       <c r="D30" t="n">
-        <v>9.10893953720494</v>
+        <v>1.480202674795803</v>
       </c>
       <c r="E30" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F30" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>22.98791953275556</v>
+        <v>3.735536924072778</v>
       </c>
       <c r="D31" t="n">
-        <v>23.23805922295801</v>
+        <v>3.776184623730677</v>
       </c>
       <c r="E31" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F31" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>34.68765000620191</v>
+        <v>5.636743126007811</v>
       </c>
       <c r="D32" t="n">
-        <v>39.16234074859052</v>
+        <v>6.36388037164596</v>
       </c>
       <c r="E32" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F32" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>22.50501026871982</v>
+        <v>3.657064168666971</v>
       </c>
       <c r="D33" t="n">
-        <v>25.87967149037452</v>
+        <v>4.20544661718586</v>
       </c>
       <c r="E33" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F33" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>35.98149947108506</v>
+        <v>5.846993664051322</v>
       </c>
       <c r="D34" t="n">
-        <v>36.04999873955732</v>
+        <v>5.858124795178066</v>
       </c>
       <c r="E34" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F34" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>12.38118205234726</v>
+        <v>2.01194208350643</v>
       </c>
       <c r="D35" t="n">
-        <v>37.2392528467888</v>
+        <v>6.05137858760318</v>
       </c>
       <c r="E35" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F35" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>47.56370476575059</v>
+        <v>7.729102024434471</v>
       </c>
       <c r="D36" t="n">
-        <v>47.6596304232948</v>
+        <v>7.744689943785406</v>
       </c>
       <c r="E36" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F36" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>41.37288225619631</v>
+        <v>6.723093366631901</v>
       </c>
       <c r="D37" t="n">
-        <v>53.8252844173029</v>
+        <v>8.746608717811721</v>
       </c>
       <c r="E37" t="n">
-        <v>10.77390243155547</v>
+        <v>1.750759145127764</v>
       </c>
       <c r="F37" t="n">
-        <v>12.03716596664725</v>
+        <v>1.956039469580178</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
